--- a/WAIC2026-北外滩双夜方案/WAIC2026北外滩双夜活动整合方案.xlsx
+++ b/WAIC2026-北外滩双夜方案/WAIC2026北外滩双夜活动整合方案.xlsx
@@ -492,7 +492,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>「AI × 城市未来 · 北外滩之夜」双夜活动整合方案 · 总览</t>
+          <t>「WAIC UP! 北外滩之夜」双夜活动整合方案 · 总览</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>「AI × 城市未来 · 北外滩之夜」（WAIC 2026 Side Events）</t>
+          <t>「WAIC UP! 北外滩之夜」（WAIC 2026 Side Events · DAY &amp; NIGHT 系列风格）</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>WAIC 白天看展、晚上到北外滩“把 AI 谈进产业与城市”</t>
+          <t>白天在展馆理解模型，晚上到北外滩追问 AI 的下一步</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>AI × 产业落地 / 城市空间 / 人居未来（与官方夜场错位：创作、开发者社区、全球游牧者、产品测评、音综均已被占坑）</t>
+          <t>Day1：AI 产业落地与建造者社交；Day2：AGI 前沿思辨（模型下一步 / 智能体 / AI for Science / 安全与治理）。与官方夜场错位：创作、开发者社区、全球游牧者、产品测评、音综均已被占坑</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>17 日“社交暖身型”先破圈、积累人脉与报名池；18 日“深度干货型”承接，把认识的人沉淀成深度讨论，形成两晚闭环</t>
+          <t>17 日“社交暖身型”先破圈、积累人脉与报名池；18 日“深度思辨型”承接，把认识的人沉淀成深度讨论，形成两晚闭环</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>杨浦联合会：大创智、在线新经济生态园、环高校科技企业群、投融资与产业对接网络（对应 Day 1）；复旦住房政策研究中心：城市与住房政策研究、学术权威、专家与校友网络（对应 Day 2）</t>
+          <t>杨浦联合会：大创智、在线新经济生态园、环高校科技企业群、投融资与产业对接网络（对应 Day 1）；复旦大学：顶尖高校 AI 学术底蕴、教授与研究员网络、庞大校友圈（对应 Day 2）</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>滨江夜景（社交与夜谈最佳背景）；北外滩本身是城市更新样本，“AI × 城市人居”议题现场即案例；主厅+露台+分区可同时支撑两种活动形态</t>
+          <t>滨江夜景与陆家嘴天际线（社交与深夜思辨最佳背景）；主厅+露台+分区可同时支撑“大场社交”与“圆桌+学术酒吧”两种形态</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>「用白天理解模型，用晚上追问产业与城市」「把 AI 谈进北外滩的夜色里」</t>
+          <t>「用白天理解机器和模型，在晚上追问 AI 的下一步」「把 AI 谈进北外滩的夜色里」</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>7月17日 Day1 · AI 产业创造者之夜</t>
+          <t>7月17日 Day1 · AI Builders Night 建造者之夜</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>7月18日 Day2 · AI 人居未来之夜</t>
+          <t>7月18日 Day2 · 通往 AGI 之夜</t>
         </is>
       </c>
     </row>
@@ -695,12 +695,12 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>暖身 · 社交 · 产业连接（横向、广）</t>
+          <t>暖身 · 社交 · 建造者连接（横向、广）</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>深度 · 学术 · 城市人居（纵向、专）</t>
+          <t>深度 · 思辨 · AI 前沿（纵向、专）</t>
         </is>
       </c>
     </row>
@@ -717,141 +717,158 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心主导</t>
+          <t>复旦大学（学术资源）主导</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>核心主题</t>
+          <t>核心一问</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>AI 落进产业与城市：「你今年在造什么？」</t>
+          <t>「你今年在造什么？」(What are you building this year?)</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>AI 如何重塑城市、空间与人的居住？</t>
+          <t>「AI 的下一步会发生什么？」</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>主打形式</t>
+          <t>核心议题</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>闪电演讲 + 1 分钟快闪开放麦 + Mixer 社交</t>
+          <t>AI 产品、创业、出海、开源、投融资</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>跨界圆桌 Panel + 学术酒吧围炉</t>
+          <t>大模型下一步、智能体、AI for Science、安全对齐与治理</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>目标受众</t>
+          <t>主打形式</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>创业者 / 科技企业 / 开发者 / 投资人</t>
+          <t>闪电演讲 + 1 分钟快闪开放麦 + Mixer 社交</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>学者 / 政策 / 城市与地产 / AI 产业领袖</t>
+          <t>跨界圆桌 Panel + 学术酒吧围炉</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>建议规模</t>
+          <t>目标受众</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>120–150 人（开放报名 + 定向邀请）</t>
+          <t>创业者 / 开发者 / 产品经理 / 投资人</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>80–100 人（以定向邀请为主，精品化）</t>
+          <t>学者 / 研究员 / AI 企业领袖 / 深度从业者</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>现场氛围</t>
+          <t>建议规模</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>灵感盲盒、松弛微醺、快节奏</t>
+          <t>120–150 人（开放报名 + 定向邀请）</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>严肃但松弛、思想碰撞、慢深度</t>
+          <t>80–100 人（以定向邀请为主，精品化）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>参考对标</t>
+          <t>现场氛围</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>AI Founders Mixer / WAIC Afterparty</t>
+          <t>灵感盲盒、松弛微醺、快节奏</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>AI 创作者之夜（错位到“人居”而非“创作”）</t>
+          <t>严肃但松弛、思想碰撞、慢深度</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>报名门槛</t>
+          <t>参考对标</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>低门槛，拉新扩圈</t>
+          <t>AI Founders Mixer / WAIC Afterparty / AI 创造者之夜</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>定向邀请为主，控质量</t>
+          <t>AI 创作者之夜（议题错位到“AGI 前沿”而非“内容创作”）</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>报名门槛</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>低门槛，拉新扩圈</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>定向邀请为主，控质量</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
           <t>时间</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>18:30–21:30（散场后无缝承接）</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>19:00–21:30（散场后无缝承接）</t>
         </is>
@@ -883,7 +900,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Day 1 · 7月17日晚「AI 产业创造者之夜」议程（18:30–21:30 · 120–150人）</t>
+          <t>Day 1 · 7月17日晚「AI Builders Night · 建造者之夜」议程（18:30–21:30 · 120–150人）</t>
         </is>
       </c>
     </row>
@@ -934,7 +951,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>杨浦区科技企业联合会 + 复旦住房政策研究中心双主办致辞，介绍系列与玩法规则</t>
+          <t>双主办致辞，介绍系列与玩法规则</t>
         </is>
       </c>
     </row>
@@ -951,7 +968,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>① AI 产业落地实战；② AI 出海最新观察；③ 爆款 AI 产品拆解；④ 杨浦 / 大创智 AI 生态案例</t>
+          <t>① AI 产品从 Demo 到 PMF 的实战；② AI 出海最新观察；③ 爆款 AI 应用拆解；④ 开源 / Agent 生态增长经验</t>
         </is>
       </c>
     </row>
@@ -985,7 +1002,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>3–4 位企业与投资嘉宾，现场 Ask Me Anything</t>
+          <t>3–4 位创业与投资嘉宾，现场 Ask Me Anything</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1019,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>无固定座位；设“企业对接区 / 投资人蹲项目区 / 复旦成果转化区”</t>
+          <t>无固定座位；设“投资人蹲项目区 / 企业对接区 / 招聘与找搭档区”</t>
         </is>
       </c>
     </row>
@@ -1019,7 +1036,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>杨浦/大创智 AI 企业创始人、AI 出海创业者、开源 Maintainer / 独立开发者、资深 AI 投资人、复旦学者（连接次日深度场）</t>
+          <t>AI 应用 / Agent 创业者、AI 出海创业者、开源 Maintainer / 独立开发者、资深 AI 投资人、大模型 / Infra 技术负责人</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1083,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Day 2 · 7月18日晚「AI 人居未来之夜」议程（19:00–21:30 · 80–100人）</t>
+          <t>Day 2 · 7月18日晚「通往 AGI 之夜」议程（19:00–21:30 · 80–100人）</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1117,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>滨江晚宴式茶歇；发放“城市之问”话题卡，引导入场即思考</t>
+          <t>滨江晚宴式茶歇；发放“AGI 之问”话题卡，入场即思考</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1134,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>复旦住房政策研究中心主任 / 教授致辞，抛出核心议题</t>
+          <t>复旦学者致辞定调，抛出核心议题</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1151,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>“AI × 城市 / 住房 / 空间”跨界圆桌：学者 + AI 技术 + 城市更新 / 地产 + 政策，站在链条不同位置展开</t>
+          <t>「通往 AGI 的路上，我们走到哪了？」——学者 × 大模型企业 × 智能体产品 × 投资人，站在链条不同位置展开</t>
         </is>
       </c>
     </row>
@@ -1151,7 +1168,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>3 桌轮换：① AI 与城市治理；② AI 与住房 / 空间；③ AI 与产业和就业，用知识下酒</t>
+          <t>3 桌轮换：① 模型桌（Scaling 之后：架构、推理、端侧）；② 智能体桌（Agent 元年之后：工作流、评测、商业化）；③ 科学与治理桌（AI for Science、安全对齐、开源与监管），用知识下酒</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1185,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>现场提问与辩题投票，无标准答案的开放讨论</t>
+          <t>现场提问与辩题投票（示例辩题：「通往 AGI，缺的是算力还是想法？」），无标准答案的开放讨论</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1202,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>滨江夜景下的深度连接，沉淀 17 日与 18 日的人脉</t>
+          <t>滨江夜景下的深度连接，沉淀两晚人脉</t>
         </is>
       </c>
     </row>
@@ -1202,7 +1219,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>AI 让城市更宜居还是加剧不平等？大模型与智能体如何进入城市治理与住房政策？数字空间与物理空间融合后的居住与办公？AI 产业变迁如何重塑就业与人口分布？</t>
+          <t>Scaling Law 之后大模型的下一步？智能体从 Demo 到可信赖生产力还差几步？AI 会先在哪个学科点燃下一次科学革命？安全、对齐与治理如何跟上能力曲线？</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1236,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>复旦住房政策研究中心学者（主持/定调）、城市规划/城市更新专家、地产/空间科技（PropTech）企业代表、AI 技术或大模型产品方、政策/公共治理方向嘉宾</t>
+          <t>复旦 AI 方向学者（主持/定调）、大模型公司研究/技术负责人、智能体（Agent）产品创始人、AI for Science 研究员、AI 安全/治理方向学者或投资人</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1253,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>复旦学术背书赋予稀缺性；北外滩城市更新样本“现场即案例”；无 PPT 学术酒吧；学者×技术×产业×政策跨界同桌</t>
+          <t>复旦学术定调赋予稀缺性；无 PPT 学术酒吧；学者×模型企业×产品×投资跨界同桌；辩题投票观众即参与者</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1351,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>白天理解模型与产品，晚上把技术带进“产业落地”（17日）与“城市人居”（18日）的具体场景</t>
+          <t>Day1 把白天看到的 Demo 与发布拉到“真实落地”检验；Day2 把白天的技术发布沉淀为“AI 下一步”的深度追问</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1385,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>「用白天理解模型，用晚上追问产业与城市」</t>
+          <t>「用白天理解机器和模型，在晚上追问 AI 的下一步」</t>
         </is>
       </c>
     </row>
@@ -1385,7 +1402,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>现场设“两晚连票 / 连报”通道，17 日到场者定向邀约 18 日深度场</t>
+          <t>设“两晚连票 / 连报”通道，17 日到场者定向邀约 18 日深度场</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1436,7 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>17 日“产业在造什么”→ 18 日“这些产业与技术将如何改变城市与人居”</t>
+          <t>17 日「大家在造什么」→ 18 日「这些正在造的东西，会把 AI 带向哪里」</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1453,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>两晚均双方共同主办，各自牵头一晚，资源互补（杨浦企业 × 复旦学术）</t>
+          <t>两晚均双方共同主办，各自牵头一晚，资源互补（杨浦产业动员 × 复旦学术定调）</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1470,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>统一使用「AI × 城市未来 · 北外滩之夜」系列视觉与话术</t>
+          <t>统一使用「WAIC UP! 北外滩之夜」系列视觉与话术</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1552,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>Day1：“What are you building”入场名牌；Day2：“城市之问”话题卡、辩题投票牌</t>
+          <t>Day1：“What are you building”入场名牌；Day2：“AGI 之问”话题卡、辩题投票牌</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1576,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>定制笔记本 / AI 名片 / 徽章（可结合复旦与杨浦元素）</t>
+          <t>定制笔记本 / AI 名片 / 徽章</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1624,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>「用白天理解模型，用晚上追问产业与城市」「把 AI 谈进北外滩的夜色里」「第一晚认识正在造 AI 的人；第二晚想清楚 AI 会把城市带向哪里」</t>
+          <t>「用白天理解机器和模型，在晚上追问 AI 的下一步」「把 AI 谈进北外滩的夜色里」「第一晚认识正在造 AI 的人；第二晚想清楚 AI 会走向哪里」</t>
         </is>
       </c>
     </row>
@@ -1631,7 +1648,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>AI × 城市未来 · 北外滩之夜 / 一滴水 · AI 夜话 / WAIC UP! 北外滩之夜</t>
+          <t>WAIC UP! 北外滩之夜 / 一滴水 · AI 之夜 / AI Nightfall 北外滩</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1660,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>AI 产业创造者之夜 / 北外滩 AI Builders Night / 你今年在造什么 · 产业夜</t>
+          <t>AI Builders Night 建造者之夜 / 你今年在造什么 · AI 之夜 / 北外滩 AI Mixer</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1672,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>AI 人居未来之夜 / AI × City &amp; Living Night / 城市之问 · AI 深夜圆桌</t>
+          <t>通往 AGI 之夜 / AI 的下一步 · 深夜圆桌 / AGI 之问 · 学术酒吧夜</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1775,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Day1 邀请 4–6 位跨圈层嘉宾（企业 / 出海 / 开源 / 投资 / 学者）</t>
+          <t>Day1 邀请 4–6 位跨圈层嘉宾（应用创业 / 出海 / 开源 / 投资 / 模型技术）</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1778,12 +1795,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>Day2 邀请 5 位跨界圆桌嘉宾（学者 / 城市 / 地产 / AI / 政策）</t>
+          <t>Day2 邀请 5 位跨界圆桌嘉宾（学者 / 大模型 / 智能体 / AI for Science / 安全治理）</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心</t>
+          <t>复旦大学（学术资源）</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -1903,7 +1920,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>复旦大学住房政策研究中心</t>
+          <t>双方共同</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
